--- a/alimenti.xlsx
+++ b/alimenti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-83" yWindow="83" windowWidth="9766" windowHeight="11280" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="carboidrati" sheetId="1" state="visible" r:id="rId1"/>
@@ -460,10 +460,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="15.796875" customWidth="1" min="1" max="1"/>
+    <col width="15.86328125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -639,7 +639,71 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gnocchi</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>crackers integrali</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>panbauletto rustico</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -653,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="19.265625" customWidth="1" min="1" max="1"/>
@@ -776,11 +840,15 @@
       <c r="C6" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1.8</v>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -912,7 +980,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>piselli in latta</t>
         </is>
@@ -998,37 +1066,37 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>salmone fresco</t>
+          <t>fiocchi di latte</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1125,6 +1193,7 @@
       <c r="E23" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="G23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1152,19 +1221,21 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>8</v>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8.7</t>
         </is>
       </c>
     </row>
@@ -1190,16 +1261,46 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bresaola</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lenticchie </t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1216,8 +1317,10 @@
       <c r="D29" t="n">
         <v>24</v>
       </c>
-      <c r="E29" t="n">
-        <v>1.2</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1227,16 +1330,102 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>simmenthal</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>seitan</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>yogurt greco intero</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ricotta</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>146</v>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1437,6 +1626,9 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+    </row>
     <row r="10">
       <c r="I10" s="2" t="n"/>
     </row>
@@ -1461,6 +1653,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="360" verticalDpi="360"/>
 </worksheet>
 </file>
 
